--- a/data/Expenses_Template.xlsx
+++ b/data/Expenses_Template.xlsx
@@ -1,13 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="📖 Guide" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Lists" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MasterData" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Monthly Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Dashboard" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📖 Guide" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MasterData" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cycles" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1210,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A2:F54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" style="114" min="1" max="1"/>
@@ -16490,4 +16491,30 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>StartDate</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/Expenses_Template.xlsx
+++ b/data/Expenses_Template.xlsx
@@ -1211,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F54"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" style="114" min="1" max="1"/>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D1" s="0" t="inlineStr">
         <is>
-          <t>Budget (PLN)</t>
+          <t>Budget (base)</t>
         </is>
       </c>
       <c r="E1" s="39" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="L1" s="40" t="inlineStr">
         <is>
-          <t>Value (PLN)</t>
+          <t>Value (base)</t>
         </is>
       </c>
     </row>
@@ -14442,6 +14442,7 @@
         <v/>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="114">
       <c r="A4" s="90" t="inlineStr">
         <is>
@@ -14512,6 +14513,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="19.5" customHeight="1" s="114">
       <c r="A9" s="90" t="inlineStr">
         <is>
@@ -16503,12 +16505,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>StartDate</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>Label</t>
         </is>

--- a/data/Expenses_Template.xlsx
+++ b/data/Expenses_Template.xlsx
@@ -1211,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A2:F54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" style="114" min="1" max="1"/>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="I1" s="40" t="inlineStr">
         <is>
-          <t>Rate to PLN</t>
+          <t>Rate to base</t>
         </is>
       </c>
       <c r="M1" s="123" t="inlineStr">
@@ -14442,7 +14442,6 @@
         <v/>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="114">
       <c r="A4" s="90" t="inlineStr">
         <is>
@@ -14513,7 +14512,6 @@
         <v/>
       </c>
     </row>
-    <row r="8"/>
     <row r="9" ht="19.5" customHeight="1" s="114">
       <c r="A9" s="90" t="inlineStr">
         <is>

--- a/data/Expenses_Template.xlsx
+++ b/data/Expenses_Template.xlsx
@@ -2980,7 +2980,7 @@
       </c>
       <c r="D1" s="0" t="inlineStr">
         <is>
-          <t>Budget (PLN)</t>
+          <t>Budget (base)</t>
         </is>
       </c>
       <c r="E1" s="39" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="I1" s="40" t="inlineStr">
         <is>
-          <t>Rate to PLN</t>
+          <t>Rate to base</t>
         </is>
       </c>
       <c r="M1" s="123" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="L1" s="40" t="inlineStr">
         <is>
-          <t>Value (PLN)</t>
+          <t>Value (base)</t>
         </is>
       </c>
     </row>
@@ -16503,12 +16503,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>StartDate</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>Label</t>
         </is>

--- a/data/Expenses_Template.xlsx
+++ b/data/Expenses_Template.xlsx
@@ -1211,7 +1211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F54"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" style="114" min="1" max="1"/>
@@ -14438,10 +14438,11 @@
         </is>
       </c>
       <c r="N2" s="89">
-        <f>IFERROR(VLOOKUP($F$2,Lists!$H$2:$I$100,2,0),1)</f>
-        <v/>
-      </c>
-    </row>
+        <f>IFERROR(VLOOKUP($F$2,Lists!$H$2:$I$1048576,2,0),1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="114">
       <c r="A4" s="90" t="inlineStr">
         <is>
@@ -14478,15 +14479,15 @@
     </row>
     <row r="6" ht="30" customHeight="1" s="114">
       <c r="B6" s="93">
-        <f>(SUMIFS(MasterData!$L$2:$L$2000,MasterData!$E$2:$E$2000,"Income",MasterData!$J$2:$J$2000,TRUE))/($N$2)</f>
+        <f>(SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$E$2:$E$1048576,"Income",MasterData!$J$2:$J$1048576,TRUE))/($N$2)</f>
         <v/>
       </c>
       <c r="C6" s="93">
-        <f>(SUMIFS(MasterData!$L$2:$L$2000,MasterData!$E$2:$E$2000,"Expense",MasterData!$J$2:$J$2000,TRUE))/($N$2)</f>
+        <f>(SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$E$2:$E$1048576,"Expense",MasterData!$J$2:$J$1048576,TRUE))/($N$2)</f>
         <v/>
       </c>
       <c r="D6" s="93">
-        <f>(SUMIFS(MasterData!$L$2:$L$2000,MasterData!$E$2:$E$2000,"Savings",MasterData!$J$2:$J$2000,TRUE))/($N$2)</f>
+        <f>(SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$E$2:$E$1048576,"Savings",MasterData!$J$2:$J$1048576,TRUE))/($N$2)</f>
         <v/>
       </c>
       <c r="E6" s="93">
@@ -14512,6 +14513,7 @@
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="19.5" customHeight="1" s="114">
       <c r="A9" s="90" t="inlineStr">
         <is>
@@ -14540,7 +14542,7 @@
         </is>
       </c>
       <c r="B10" s="95">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$E$2:$E$2000,"Income",MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$E$2:$E$2000,"Income",MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$E$2:$E$1048576,"Income",MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$E$2:$E$1048576,"Income",MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="H10" s="96" t="inlineStr">
@@ -14576,7 +14578,7 @@
         </is>
       </c>
       <c r="B11" s="95">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$E$2:$E$2000,"Expense",MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$E$2:$E$2000,"Expense",MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$E$2:$E$1048576,"Expense",MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$E$2:$E$1048576,"Expense",MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="H11" s="97" t="inlineStr">
@@ -14585,11 +14587,11 @@
         </is>
       </c>
       <c r="I11" s="98">
-        <f>IFERROR(VLOOKUP(H11,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H11,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J11" s="71">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H11,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H11,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H11,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H11,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K11" s="99">
@@ -14608,7 +14610,7 @@
         </is>
       </c>
       <c r="B12" s="95">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$E$2:$E$2000,"Savings",MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$E$2:$E$2000,"Savings",MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$E$2:$E$1048576,"Savings",MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$E$2:$E$1048576,"Savings",MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="H12" s="101" t="inlineStr">
@@ -14617,11 +14619,11 @@
         </is>
       </c>
       <c r="I12" s="102">
-        <f>IFERROR(VLOOKUP(H12,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H12,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J12" s="68">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H12,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H12,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H12,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H12,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K12" s="103">
@@ -14649,11 +14651,11 @@
         </is>
       </c>
       <c r="I13" s="98">
-        <f>IFERROR(VLOOKUP(H13,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H13,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J13" s="71">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H13,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H13,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H13,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H13,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K13" s="99">
@@ -14681,11 +14683,11 @@
         </is>
       </c>
       <c r="I14" s="102">
-        <f>IFERROR(VLOOKUP(H14,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H14,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J14" s="68">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H14,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H14,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H14,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H14,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K14" s="103">
@@ -14713,11 +14715,11 @@
         </is>
       </c>
       <c r="I15" s="98">
-        <f>IFERROR(VLOOKUP(H15,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H15,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J15" s="71">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H15,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H15,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H15,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H15,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K15" s="99">
@@ -14736,11 +14738,11 @@
         </is>
       </c>
       <c r="I16" s="102">
-        <f>IFERROR(VLOOKUP(H16,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H16,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J16" s="68">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H16,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H16,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H16,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H16,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K16" s="103">
@@ -14759,11 +14761,11 @@
         </is>
       </c>
       <c r="I17" s="98">
-        <f>IFERROR(VLOOKUP(H17,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H17,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J17" s="71">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H17,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H17,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H17,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H17,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K17" s="99">
@@ -14782,11 +14784,11 @@
         </is>
       </c>
       <c r="I18" s="102">
-        <f>IFERROR(VLOOKUP(H18,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H18,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J18" s="68">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H18,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H18,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H18,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H18,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K18" s="103">
@@ -14811,11 +14813,11 @@
         </is>
       </c>
       <c r="I19" s="98">
-        <f>IFERROR(VLOOKUP(H19,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H19,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J19" s="71">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H19,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H19,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H19,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H19,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K19" s="99">
@@ -14865,11 +14867,11 @@
         </is>
       </c>
       <c r="I20" s="102">
-        <f>IFERROR(VLOOKUP(H20,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H20,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J20" s="68">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H20,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H20,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H20,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H20,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K20" s="103">
@@ -14913,11 +14915,11 @@
         </is>
       </c>
       <c r="I21" s="98">
-        <f>IFERROR(VLOOKUP(H21,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H21,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J21" s="71">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H21,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H21,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H21,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H21,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K21" s="99">
@@ -14961,11 +14963,11 @@
         </is>
       </c>
       <c r="I22" s="102">
-        <f>IFERROR(VLOOKUP(H22,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H22,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J22" s="68">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H22,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H22,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H22,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H22,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K22" s="103">
@@ -15009,11 +15011,11 @@
         </is>
       </c>
       <c r="I23" s="98">
-        <f>IFERROR(VLOOKUP(H23,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H23,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J23" s="71">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H23,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H23,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H23,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H23,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K23" s="99">
@@ -15057,11 +15059,11 @@
         </is>
       </c>
       <c r="I24" s="102">
-        <f>IFERROR(VLOOKUP(H24,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H24,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J24" s="68">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H24,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H24,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H24,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H24,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K24" s="103">
@@ -15105,11 +15107,11 @@
         </is>
       </c>
       <c r="I25" s="98">
-        <f>IFERROR(VLOOKUP(H25,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H25,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J25" s="71">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H25,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H25,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H25,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H25,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K25" s="99">
@@ -15153,11 +15155,11 @@
         </is>
       </c>
       <c r="I26" s="102">
-        <f>IFERROR(VLOOKUP(H26,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H26,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J26" s="68">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H26,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H26,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H26,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H26,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K26" s="103">
@@ -15201,11 +15203,11 @@
         </is>
       </c>
       <c r="I27" s="98">
-        <f>IFERROR(VLOOKUP(H27,Lists!$C$2:$D$100,2,0),0)/$N$2</f>
+        <f>IFERROR(VLOOKUP(H27,Lists!$C$2:$D$1048576,2,0),0)/$N$2</f>
         <v/>
       </c>
       <c r="J27" s="71">
-        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H27,MasterData!$B$2:$B$2000,$B$2,MasterData!$J$2:$J$2000,TRUE),SUMIFS(MasterData!$L$2:$L$2000,MasterData!$F$2:$F$2000,H27,MasterData!$B$2:$B$2000,$B$2,MasterData!$C$2:$C$2000,$D$2,MasterData!$J$2:$J$2000,TRUE)))/($N$2)</f>
+        <f>(IF($D$2="",SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H27,MasterData!$B$2:$B$1048576,$B$2,MasterData!$J$2:$J$1048576,TRUE),SUMIFS(MasterData!$L$2:$L$1048576,MasterData!$F$2:$F$1048576,H27,MasterData!$B$2:$B$1048576,$B$2,MasterData!$C$2:$C$1048576,$D$2,MasterData!$J$2:$J$1048576,TRUE)))/($N$2)</f>
         <v/>
       </c>
       <c r="K27" s="99">
